--- a/data/trans_orig/IP18B2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP18B2-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>55,02%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,8%</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3410</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2349,12 +2349,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3984</t>
+          <t>3953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>666</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2399,12 +2399,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3179,12 +3179,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>56,38%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>2233</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3663</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2731</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>56,34%</t>
+          <t>56,86%</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2235</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>2697</t>
+          <t>2695</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>688</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>702</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -7863,12 +7863,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7898,12 +7898,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7933,12 +7933,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7948,12 +7948,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,25%</t>
         </is>
       </c>
     </row>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3451</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8561,7 +8561,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>2822</t>
+          <t>2497</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -8654,12 +8654,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -8669,12 +8669,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2558</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>3092</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3437</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>2716</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -9372,7 +9372,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3125</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -9450,7 +9450,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="S81" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>744</t>
         </is>
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3218</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="T83" s="2" t="inlineStr">
         <is>
-          <t>3572</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="U83" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -10315,7 +10315,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>460</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>47,25%</t>
         </is>
       </c>
     </row>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -10993,7 +10993,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -11184,7 +11184,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>2739</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -11749,7 +11749,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -11784,7 +11784,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>2537</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3784</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -11912,7 +11912,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>43,7%</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -12427,7 +12427,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -12457,12 +12457,12 @@
       </c>
       <c r="S107" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>520</t>
         </is>
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -12472,12 +12472,12 @@
       </c>
       <c r="V107" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>47,86%</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12622,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -12707,7 +12707,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12883,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>4240</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -13561,7 +13561,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="N117" s="2" t="inlineStr">
@@ -13576,7 +13576,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="W117" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
@@ -13689,7 +13689,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -13709,7 +13709,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="W118" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="J121" s="2" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
@@ -14063,7 +14063,7 @@
       </c>
       <c r="W121" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -14219,7 +14219,7 @@
       </c>
       <c r="I123" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="J123" s="2" t="inlineStr">
@@ -14239,7 +14239,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2666</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -14269,12 +14269,12 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -14284,12 +14284,12 @@
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>2766</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="W126" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14769,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -14819,7 +14819,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -14834,12 +14834,12 @@
       </c>
       <c r="S128" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -14849,12 +14849,12 @@
       </c>
       <c r="V128" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>46,86%</t>
         </is>
       </c>
     </row>
@@ -14994,12 +14994,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>10337</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -15009,12 +15009,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -15029,12 +15029,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>7051</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -15044,12 +15044,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -15079,12 +15079,12 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J131" s="2" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="W131" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -15255,12 +15255,12 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -15270,12 +15270,12 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -15290,12 +15290,12 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -15305,12 +15305,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -15672,12 +15672,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>5088</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -15687,12 +15687,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -15727,7 +15727,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -15742,12 +15742,12 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -15785,12 +15785,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>9475</t>
+          <t>8754</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -15800,12 +15800,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -15820,12 +15820,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -15835,12 +15835,12 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -15855,12 +15855,12 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>13715</t>
+          <t>13457</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -15870,12 +15870,12 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>3418</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
@@ -15933,12 +15933,12 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>633</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -15948,12 +15948,12 @@
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -15968,12 +15968,12 @@
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>5908</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="U138" s="2" t="inlineStr">
@@ -15983,12 +15983,12 @@
       </c>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -16031,7 +16031,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -16081,12 +16081,12 @@
       </c>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="U139" s="2" t="inlineStr">
@@ -16101,7 +16101,7 @@
       </c>
       <c r="W139" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3771</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
@@ -16144,7 +16144,7 @@
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="T140" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="U140" s="2" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -16370,7 +16370,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
@@ -16440,7 +16440,7 @@
       </c>
       <c r="W142" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -16468,7 +16468,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>6454</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -16483,7 +16483,7 @@
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -16498,12 +16498,12 @@
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -16513,12 +16513,12 @@
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -16533,12 +16533,12 @@
       </c>
       <c r="S143" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
@@ -16548,12 +16548,12 @@
       </c>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -16576,12 +16576,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -16591,12 +16591,12 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -16611,12 +16611,12 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -16626,12 +16626,12 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -16646,12 +16646,12 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>5128</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -16661,12 +16661,12 @@
       </c>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -16729,7 +16729,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4044</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="T145" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="U145" s="2" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="W145" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -16842,7 +16842,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -16857,7 +16857,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>3272</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="W146" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -16990,7 +16990,7 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -17005,7 +17005,7 @@
       </c>
       <c r="W147" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -17141,12 +17141,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>3526</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>10351</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -17156,12 +17156,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -17176,12 +17176,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2636</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9421</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -17191,12 +17191,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -17211,12 +17211,12 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>17624</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -17226,12 +17226,12 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -17645,7 +17645,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -17660,7 +17660,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -17680,7 +17680,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -17866,12 +17866,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -17901,12 +17901,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -17916,12 +17916,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -18358,7 +18358,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>24,78%</t>
         </is>
       </c>
     </row>
@@ -18401,7 +18401,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -18486,7 +18486,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -19079,7 +19079,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -19094,7 +19094,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -19164,7 +19164,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2786</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -19207,7 +19207,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -19262,7 +19262,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2480</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -19277,7 +19277,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3992</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>36,09%</t>
         </is>
       </c>
     </row>
@@ -19757,7 +19757,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -19787,12 +19787,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -19802,12 +19802,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -19822,12 +19822,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>51,94%</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20022,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -20037,7 +20037,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -20052,12 +20052,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -20067,12 +20067,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -20248,7 +20248,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2844</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -20298,7 +20298,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -20700,7 +20700,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -20715,7 +20715,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -20750,7 +20750,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20813,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3252</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -20848,7 +20848,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -20863,7 +20863,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -21413,7 +21413,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -21428,7 +21428,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -22169,7 +22169,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -22184,7 +22184,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -22219,7 +22219,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,05%</t>
         </is>
       </c>
     </row>
@@ -22590,7 +22590,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2775</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -22605,7 +22605,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3361</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -22655,12 +22655,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -22670,12 +22670,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>61,44%</t>
         </is>
       </c>
     </row>
@@ -23077,7 +23077,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -23092,7 +23092,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -23112,7 +23112,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3967</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -23981,7 +23981,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3299</t>
+          <t>2706</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -23996,7 +23996,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -24011,12 +24011,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>592</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -24026,12 +24026,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>59,65%</t>
         </is>
       </c>
     </row>
@@ -24511,7 +24511,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -24546,7 +24546,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -24561,7 +24561,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -24596,7 +24596,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,98%</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -24771,12 +24771,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>741</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6288</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -24786,12 +24786,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -24806,12 +24806,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -24821,12 +24821,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -24962,12 +24962,12 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>5635</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -24977,12 +24977,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -24997,12 +24997,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>1674</t>
+          <t>1534</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>7563</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -25012,12 +25012,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -25032,12 +25032,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3584</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -25047,12 +25047,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -25193,7 +25193,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>2658</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -25208,7 +25208,7 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -25263,7 +25263,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -25278,7 +25278,7 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -25419,7 +25419,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -25434,7 +25434,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -25449,12 +25449,12 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -25464,12 +25464,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -25484,12 +25484,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,29%</t>
         </is>
       </c>
     </row>
@@ -25527,12 +25527,12 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -25542,12 +25542,12 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -25597,12 +25597,12 @@
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -25612,12 +25612,12 @@
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -25758,7 +25758,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -25828,7 +25828,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -26034,7 +26034,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="T78" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="U78" s="2" t="inlineStr">
@@ -26069,7 +26069,7 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -26210,7 +26210,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -26225,7 +26225,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -26245,7 +26245,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -26260,7 +26260,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -26275,12 +26275,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5506</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -26290,12 +26290,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -26323,7 +26323,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -26338,7 +26338,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -26373,7 +26373,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -26775,7 +26775,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3286</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -26790,7 +26790,7 @@
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="T85" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="U85" s="2" t="inlineStr">
@@ -26860,7 +26860,7 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -26888,7 +26888,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -26903,7 +26903,7 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
@@ -26918,12 +26918,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5672</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -26933,12 +26933,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -26953,12 +26953,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -26968,12 +26968,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -27118,7 +27118,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -27153,7 +27153,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>57,1%</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -27183,12 +27183,12 @@
       </c>
       <c r="S88" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -27198,12 +27198,12 @@
       </c>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -27344,7 +27344,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -27359,7 +27359,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>2689</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -27429,7 +27429,7 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -27457,7 +27457,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
@@ -27527,7 +27527,7 @@
       </c>
       <c r="T91" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="U91" s="2" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -27718,7 +27718,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -27753,7 +27753,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -27768,7 +27768,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -27831,7 +27831,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -27846,7 +27846,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>3571</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -27909,7 +27909,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -27924,7 +27924,7 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -27959,7 +27959,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -27974,12 +27974,12 @@
       </c>
       <c r="S95" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T95" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="U95" s="2" t="inlineStr">
@@ -27989,12 +27989,12 @@
       </c>
       <c r="V95" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -28057,7 +28057,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -28072,7 +28072,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -28092,7 +28092,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3632</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -28587,7 +28587,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>3152</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -28672,7 +28672,7 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -28735,7 +28735,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -28770,7 +28770,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -28785,7 +28785,7 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -29187,7 +29187,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
@@ -29202,7 +29202,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -29222,7 +29222,7 @@
       </c>
       <c r="T106" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U106" s="2" t="inlineStr">
@@ -29237,7 +29237,7 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -29265,7 +29265,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
@@ -29300,7 +29300,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
@@ -29315,7 +29315,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -29335,7 +29335,7 @@
       </c>
       <c r="T107" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4069</t>
         </is>
       </c>
       <c r="U107" s="2" t="inlineStr">
@@ -29350,7 +29350,7 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -29545,7 +29545,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -29580,7 +29580,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -29756,7 +29756,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
@@ -29771,7 +29771,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -29791,7 +29791,7 @@
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -29806,7 +29806,7 @@
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -30243,7 +30243,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -30258,7 +30258,7 @@
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>35,99%</t>
         </is>
       </c>
     </row>
@@ -30321,7 +30321,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
@@ -30336,7 +30336,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -30351,12 +30351,12 @@
       </c>
       <c r="S116" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>5783</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -30366,12 +30366,12 @@
       </c>
       <c r="V116" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W116" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>62,97%</t>
         </is>
       </c>
     </row>
@@ -31112,7 +31112,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -31127,7 +31127,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -31142,12 +31142,12 @@
       </c>
       <c r="S123" s="2" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>457</t>
         </is>
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -31157,12 +31157,12 @@
       </c>
       <c r="V123" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>52,3%</t>
         </is>
       </c>
     </row>
@@ -31338,7 +31338,7 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
@@ -31353,7 +31353,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -31373,7 +31373,7 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3465</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
@@ -31388,7 +31388,7 @@
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -31599,7 +31599,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
@@ -31614,7 +31614,7 @@
       </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>42,13%</t>
         </is>
       </c>
     </row>
@@ -31677,7 +31677,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>2826</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
@@ -31692,7 +31692,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -31712,7 +31712,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>3479</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -31727,7 +31727,7 @@
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>31,93%</t>
         </is>
       </c>
     </row>
@@ -31867,12 +31867,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -31882,12 +31882,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -31902,12 +31902,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12543</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -31917,12 +31917,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -31937,12 +31937,12 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -31952,12 +31952,12 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -32093,12 +32093,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>9731</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -32108,12 +32108,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -32128,12 +32128,12 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -32143,12 +32143,12 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -32163,12 +32163,12 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10263</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -32178,12 +32178,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -32211,7 +32211,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -32226,7 +32226,7 @@
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="J133" s="2" t="inlineStr">
@@ -32281,7 +32281,7 @@
       </c>
       <c r="T133" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5057</t>
         </is>
       </c>
       <c r="U133" s="2" t="inlineStr">
@@ -32296,7 +32296,7 @@
       </c>
       <c r="W133" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -32324,7 +32324,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>2495</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -32339,7 +32339,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="U134" s="2" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="W134" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -32472,7 +32472,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>3477</t>
+          <t>3646</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -32487,7 +32487,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -32507,7 +32507,7 @@
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="U135" s="2" t="inlineStr">
@@ -32522,7 +32522,7 @@
       </c>
       <c r="W135" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -32545,12 +32545,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>7529</t>
+          <t>7561</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -32560,12 +32560,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -32580,12 +32580,12 @@
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>2806</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -32595,12 +32595,12 @@
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -32615,12 +32615,12 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -32630,12 +32630,12 @@
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -32658,12 +32658,12 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -32673,12 +32673,12 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -32693,12 +32693,12 @@
       </c>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -32708,12 +32708,12 @@
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -32728,12 +32728,12 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>16302</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -32743,12 +32743,12 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -32811,7 +32811,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>3464</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -32826,7 +32826,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U138" s="2" t="inlineStr">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="W138" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -32889,7 +32889,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3624</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -32904,7 +32904,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -32959,7 +32959,7 @@
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3338</t>
         </is>
       </c>
       <c r="U139" s="2" t="inlineStr">
@@ -32974,7 +32974,7 @@
       </c>
       <c r="W139" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -33150,7 +33150,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
@@ -33165,7 +33165,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -33185,7 +33185,7 @@
       </c>
       <c r="T141" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="U141" s="2" t="inlineStr">
@@ -33200,7 +33200,7 @@
       </c>
       <c r="W141" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -33228,7 +33228,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
@@ -33243,7 +33243,7 @@
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
@@ -33298,7 +33298,7 @@
       </c>
       <c r="T142" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="U142" s="2" t="inlineStr">
@@ -33313,7 +33313,7 @@
       </c>
       <c r="W142" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -33336,12 +33336,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -33351,12 +33351,12 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -33376,7 +33376,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -33391,7 +33391,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -33406,12 +33406,12 @@
       </c>
       <c r="S143" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1528</t>
         </is>
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
@@ -33421,12 +33421,12 @@
       </c>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -33449,12 +33449,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -33464,12 +33464,12 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -33484,12 +33484,12 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -33499,12 +33499,12 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -33519,12 +33519,12 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -33534,12 +33534,12 @@
       </c>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -33715,7 +33715,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -33730,7 +33730,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -33750,7 +33750,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
@@ -33765,7 +33765,7 @@
       </c>
       <c r="W146" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -33828,7 +33828,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -33843,7 +33843,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -33863,7 +33863,7 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -33878,7 +33878,7 @@
       </c>
       <c r="W147" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -33906,7 +33906,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -33941,7 +33941,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -33971,12 +33971,12 @@
       </c>
       <c r="S148" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="U148" s="2" t="inlineStr">
@@ -33991,7 +33991,7 @@
       </c>
       <c r="W148" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -34014,12 +34014,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -34029,12 +34029,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -34049,12 +34049,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>13804</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -34064,12 +34064,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -34084,12 +34084,12 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -34099,12 +34099,12 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -34553,7 +34553,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -34568,7 +34568,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>56,48%</t>
         </is>
       </c>
     </row>
@@ -35005,7 +35005,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -35020,7 +35020,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -35344,7 +35344,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -35359,7 +35359,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -36135,7 +36135,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -36150,7 +36150,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -36587,7 +36587,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -36602,7 +36602,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -36695,12 +36695,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>725</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -36710,12 +36710,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -36895,7 +36895,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -36910,7 +36910,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -36930,7 +36930,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -36945,7 +36945,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -37121,7 +37121,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -37136,7 +37136,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -37151,12 +37151,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -37166,12 +37166,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,12%</t>
         </is>
       </c>
     </row>
@@ -37538,7 +37538,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2715</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -37553,7 +37553,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -37608,7 +37608,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2599</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -37623,7 +37623,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -37686,7 +37686,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -37701,7 +37701,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -37721,7 +37721,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -37736,7 +37736,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -37912,7 +37912,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -37927,7 +37927,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -37947,7 +37947,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -37962,7 +37962,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -38703,7 +38703,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -38718,7 +38718,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -38738,7 +38738,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -38753,7 +38753,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>42,39%</t>
         </is>
       </c>
     </row>
@@ -39007,7 +39007,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>2620</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -39077,7 +39077,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -39493,12 +39493,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4167</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -39508,12 +39508,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -39528,12 +39528,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4733</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -39543,12 +39543,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -40854,7 +40854,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>2952</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -40889,7 +40889,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3578</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -41193,7 +41193,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -41208,7 +41208,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -41228,7 +41228,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -41243,7 +41243,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,34%</t>
         </is>
       </c>
     </row>
@@ -41414,12 +41414,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -41429,12 +41429,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -41449,12 +41449,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -41464,12 +41464,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -41614,7 +41614,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -41629,7 +41629,7 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -41644,12 +41644,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5114</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -41659,12 +41659,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -41679,12 +41679,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -41694,12 +41694,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -41762,7 +41762,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>2856</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -41777,7 +41777,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -41797,7 +41797,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
@@ -41812,7 +41812,7 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -41840,7 +41840,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -41850,12 +41850,12 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -41870,12 +41870,12 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -41885,12 +41885,12 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -41905,12 +41905,12 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1820</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
@@ -41920,12 +41920,12 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -42214,7 +42214,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -42229,7 +42229,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -42249,7 +42249,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>5136</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -42264,7 +42264,7 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -42292,7 +42292,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -42307,7 +42307,7 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -42327,7 +42327,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>4494</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -42342,7 +42342,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -42357,12 +42357,12 @@
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -42372,12 +42372,12 @@
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -42405,7 +42405,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -42420,7 +42420,7 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -42440,7 +42440,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -42475,7 +42475,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -42490,7 +42490,7 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -42553,7 +42553,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -42588,7 +42588,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -42603,7 +42603,7 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -42631,7 +42631,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3503</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -42646,7 +42646,7 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -42701,7 +42701,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -42716,7 +42716,7 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -43083,7 +43083,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -43098,7 +43098,7 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -43118,7 +43118,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -43133,7 +43133,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -43148,12 +43148,12 @@
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
@@ -43163,12 +43163,12 @@
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -43196,7 +43196,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -43211,7 +43211,7 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
@@ -43231,7 +43231,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>4380</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -43246,7 +43246,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -43266,7 +43266,7 @@
       </c>
       <c r="T81" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="U81" s="2" t="inlineStr">
@@ -43281,7 +43281,7 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -43535,7 +43535,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>2660</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -43550,7 +43550,7 @@
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
@@ -43605,7 +43605,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="U84" s="2" t="inlineStr">
@@ -43620,7 +43620,7 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -43791,12 +43791,12 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -43806,12 +43806,12 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -43826,12 +43826,12 @@
       </c>
       <c r="S86" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T86" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="U86" s="2" t="inlineStr">
@@ -43841,12 +43841,12 @@
       </c>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,65%</t>
         </is>
       </c>
     </row>
@@ -43991,7 +43991,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
@@ -44061,7 +44061,7 @@
       </c>
       <c r="T88" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="U88" s="2" t="inlineStr">
@@ -44076,7 +44076,7 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -44139,7 +44139,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -44154,7 +44154,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -44174,7 +44174,7 @@
       </c>
       <c r="T89" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="U89" s="2" t="inlineStr">
@@ -44189,7 +44189,7 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44217,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>2905</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -44232,7 +44232,7 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
@@ -44252,7 +44252,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -44267,7 +44267,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -44282,12 +44282,12 @@
       </c>
       <c r="S90" s="2" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>514</t>
         </is>
       </c>
       <c r="T90" s="2" t="inlineStr">
         <is>
-          <t>5132</t>
+          <t>4498</t>
         </is>
       </c>
       <c r="U90" s="2" t="inlineStr">
@@ -44297,12 +44297,12 @@
       </c>
       <c r="V90" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>44,72%</t>
         </is>
       </c>
     </row>
@@ -44443,7 +44443,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>3338</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
@@ -44458,7 +44458,7 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
@@ -44478,7 +44478,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -44493,7 +44493,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -44513,7 +44513,7 @@
       </c>
       <c r="T92" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="U92" s="2" t="inlineStr">
@@ -44528,7 +44528,7 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -44556,7 +44556,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -44571,7 +44571,7 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
@@ -44626,7 +44626,7 @@
       </c>
       <c r="T93" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="U93" s="2" t="inlineStr">
@@ -44641,7 +44641,7 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -44669,7 +44669,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -44684,7 +44684,7 @@
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
@@ -44739,7 +44739,7 @@
       </c>
       <c r="T94" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="U94" s="2" t="inlineStr">
@@ -44754,7 +44754,7 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>39,56%</t>
         </is>
       </c>
     </row>
@@ -44930,7 +44930,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3808</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -44945,7 +44945,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -44965,7 +44965,7 @@
       </c>
       <c r="T96" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="U96" s="2" t="inlineStr">
@@ -44980,7 +44980,7 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -45460,7 +45460,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -45475,7 +45475,7 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
@@ -45530,7 +45530,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -45545,7 +45545,7 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -45912,7 +45912,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -45927,7 +45927,7 @@
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
@@ -45982,7 +45982,7 @@
       </c>
       <c r="T105" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3914</t>
         </is>
       </c>
       <c r="U105" s="2" t="inlineStr">
@@ -45997,7 +45997,7 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -46403,7 +46403,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
@@ -46418,7 +46418,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -46438,7 +46438,7 @@
       </c>
       <c r="T109" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="U109" s="2" t="inlineStr">
@@ -46453,7 +46453,7 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -46594,7 +46594,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -46609,7 +46609,7 @@
       </c>
       <c r="I111" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
@@ -46659,12 +46659,12 @@
       </c>
       <c r="S111" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>742</t>
         </is>
       </c>
       <c r="T111" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U111" s="2" t="inlineStr">
@@ -46674,12 +46674,12 @@
       </c>
       <c r="V111" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W111" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>73,55%</t>
         </is>
       </c>
     </row>
@@ -47116,7 +47116,7 @@
       </c>
       <c r="T115" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="U115" s="2" t="inlineStr">
@@ -47131,7 +47131,7 @@
       </c>
       <c r="W115" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,37%</t>
         </is>
       </c>
     </row>
@@ -47985,7 +47985,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
@@ -48000,7 +48000,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -48020,7 +48020,7 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -48035,7 +48035,7 @@
       </c>
       <c r="W123" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -48176,7 +48176,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -48191,7 +48191,7 @@
       </c>
       <c r="I125" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
@@ -48246,7 +48246,7 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
@@ -48261,7 +48261,7 @@
       </c>
       <c r="W125" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -48515,7 +48515,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
@@ -48530,7 +48530,7 @@
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
@@ -48585,7 +48585,7 @@
       </c>
       <c r="T128" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="U128" s="2" t="inlineStr">
@@ -48600,7 +48600,7 @@
       </c>
       <c r="W128" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -48740,12 +48740,12 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
@@ -48755,12 +48755,12 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
@@ -48775,12 +48775,12 @@
       </c>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
@@ -48790,12 +48790,12 @@
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -48810,12 +48810,12 @@
       </c>
       <c r="S130" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4314</t>
         </is>
       </c>
       <c r="T130" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13544</t>
         </is>
       </c>
       <c r="U130" s="2" t="inlineStr">
@@ -48825,12 +48825,12 @@
       </c>
       <c r="V130" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W130" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,09%</t>
         </is>
       </c>
     </row>
@@ -48893,7 +48893,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -48928,7 +48928,7 @@
       </c>
       <c r="T131" s="2" t="inlineStr">
         <is>
-          <t>4669</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="U131" s="2" t="inlineStr">
@@ -48943,7 +48943,7 @@
       </c>
       <c r="W131" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -48966,12 +48966,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
@@ -48981,12 +48981,12 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
@@ -49001,12 +49001,12 @@
       </c>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
@@ -49016,12 +49016,12 @@
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -49036,12 +49036,12 @@
       </c>
       <c r="S132" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="T132" s="2" t="inlineStr">
         <is>
-          <t>21037</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="U132" s="2" t="inlineStr">
@@ -49051,12 +49051,12 @@
       </c>
       <c r="V132" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -49197,7 +49197,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
@@ -49212,7 +49212,7 @@
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
@@ -49232,7 +49232,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5142</t>
         </is>
       </c>
       <c r="N134" s="2" t="inlineStr">
@@ -49247,7 +49247,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -49262,12 +49262,12 @@
       </c>
       <c r="S134" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>740</t>
         </is>
       </c>
       <c r="T134" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="U134" s="2" t="inlineStr">
@@ -49277,12 +49277,12 @@
       </c>
       <c r="V134" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W134" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -49310,7 +49310,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -49325,7 +49325,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="J135" s="2" t="inlineStr">
@@ -49345,7 +49345,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -49360,7 +49360,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -49375,12 +49375,12 @@
       </c>
       <c r="S135" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T135" s="2" t="inlineStr">
         <is>
-          <t>5982</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="U135" s="2" t="inlineStr">
@@ -49390,12 +49390,12 @@
       </c>
       <c r="V135" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W135" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -49418,12 +49418,12 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
@@ -49433,12 +49433,12 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
@@ -49458,7 +49458,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="N136" s="2" t="inlineStr">
@@ -49473,7 +49473,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -49488,12 +49488,12 @@
       </c>
       <c r="S136" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="T136" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="U136" s="2" t="inlineStr">
@@ -49503,12 +49503,12 @@
       </c>
       <c r="V136" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W136" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -49536,7 +49536,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -49551,7 +49551,7 @@
       </c>
       <c r="I137" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
@@ -49571,7 +49571,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>4552</t>
+          <t>4120</t>
         </is>
       </c>
       <c r="N137" s="2" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -49601,12 +49601,12 @@
       </c>
       <c r="S137" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>648</t>
         </is>
       </c>
       <c r="T137" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="U137" s="2" t="inlineStr">
@@ -49616,12 +49616,12 @@
       </c>
       <c r="V137" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W137" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -49679,12 +49679,12 @@
       </c>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>725</t>
         </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>6630</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
@@ -49694,12 +49694,12 @@
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -49714,12 +49714,12 @@
       </c>
       <c r="S138" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>951</t>
         </is>
       </c>
       <c r="T138" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U138" s="2" t="inlineStr">
@@ -49729,12 +49729,12 @@
       </c>
       <c r="V138" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W138" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,66%</t>
         </is>
       </c>
     </row>
@@ -49762,7 +49762,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -49777,7 +49777,7 @@
       </c>
       <c r="I139" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
@@ -49812,7 +49812,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -49827,12 +49827,12 @@
       </c>
       <c r="S139" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>543</t>
         </is>
       </c>
       <c r="T139" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="U139" s="2" t="inlineStr">
@@ -49842,12 +49842,12 @@
       </c>
       <c r="V139" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W139" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -50209,12 +50209,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>733</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>5823</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -50224,12 +50224,12 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
@@ -50249,7 +50249,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
@@ -50264,7 +50264,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -50279,12 +50279,12 @@
       </c>
       <c r="S143" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T143" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U143" s="2" t="inlineStr">
@@ -50294,12 +50294,12 @@
       </c>
       <c r="V143" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W143" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -50327,7 +50327,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
@@ -50342,7 +50342,7 @@
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
@@ -50357,12 +50357,12 @@
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
@@ -50372,12 +50372,12 @@
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -50392,12 +50392,12 @@
       </c>
       <c r="S144" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1926</t>
         </is>
       </c>
       <c r="T144" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="U144" s="2" t="inlineStr">
@@ -50407,12 +50407,12 @@
       </c>
       <c r="V144" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W144" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -50553,7 +50553,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
@@ -50568,7 +50568,7 @@
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
@@ -50588,7 +50588,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
@@ -50603,7 +50603,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -50618,12 +50618,12 @@
       </c>
       <c r="S146" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>626</t>
         </is>
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
@@ -50633,12 +50633,12 @@
       </c>
       <c r="V146" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W146" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -50661,12 +50661,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -50676,12 +50676,12 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J147" s="2" t="inlineStr">
@@ -50701,7 +50701,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
@@ -50716,7 +50716,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -50731,12 +50731,12 @@
       </c>
       <c r="S147" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>644</t>
         </is>
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5654</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -50746,12 +50746,12 @@
       </c>
       <c r="V147" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W147" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -50779,7 +50779,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
@@ -50794,7 +50794,7 @@
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
@@ -50849,7 +50849,7 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="U148" s="2" t="inlineStr">
@@ -50864,7 +50864,7 @@
       </c>
       <c r="W148" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -50887,12 +50887,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -50902,12 +50902,12 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
@@ -50922,12 +50922,12 @@
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>11185</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
@@ -50937,12 +50937,12 @@
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -50957,12 +50957,12 @@
       </c>
       <c r="S149" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>16239</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -50972,12 +50972,12 @@
       </c>
       <c r="V149" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W149" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
